--- a/valve_replacement_study_code/Diagnostics/efi_codelist_review.xlsx
+++ b/valve_replacement_study_code/Diagnostics/efi_codelist_review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\martaa\Documents\GitHub\HERON-UK-02-002-CVDValveReplacement\valve_replacement_study_code\Diagnostics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BF516B-B7E3-45C9-A929-1807D2EF7173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545F849C-7610-4C63-AC3A-7EE562D7C534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{E340D0E8-65CA-1B46-902B-CBE1C20BABCE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22245" windowHeight="13321" xr2:uid="{E340D0E8-65CA-1B46-902B-CBE1C20BABCE}"/>
   </bookViews>
   <sheets>
     <sheet name="ConceptIds" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="298">
   <si>
     <t>concept_id</t>
   </si>
@@ -55,33 +55,18 @@
     <t>comments</t>
   </si>
   <si>
-    <t>index</t>
-  </si>
-  <si>
     <t>activity_limitation</t>
   </si>
   <si>
-    <t>anaemia_and_haematinic_deficiency</t>
-  </si>
-  <si>
-    <t>anemia broad from table 1 or anemia nutritional from table 1?</t>
-  </si>
-  <si>
     <t>arthritis</t>
   </si>
   <si>
     <t>Atrial fibrillation</t>
   </si>
   <si>
-    <t>from table 1</t>
-  </si>
-  <si>
     <t>Cerebrovascular disease</t>
   </si>
   <si>
-    <t>CKD</t>
-  </si>
-  <si>
     <t>Diabetes</t>
   </si>
   <si>
@@ -130,9 +115,6 @@
     <t>Osteoporosis</t>
   </si>
   <si>
-    <t>Parkinsonism and tremor</t>
-  </si>
-  <si>
     <t>Peptic ulcer</t>
   </si>
   <si>
@@ -172,32 +154,794 @@
     <t>Weight loss and anorexia</t>
   </si>
   <si>
-    <t>same as CCI</t>
-  </si>
-  <si>
-    <t>from table 1 (ckd condition)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From table 1: Hypertension wide </t>
-  </si>
-  <si>
-    <t>From table 1: Coronary artery disease??</t>
-  </si>
-  <si>
-    <t>diabetes with complications + diabetes without complications from CCI</t>
-  </si>
-  <si>
-    <t>Same as CCI</t>
-  </si>
-  <si>
     <t>Calculated based on drug_exposure table</t>
+  </si>
+  <si>
+    <t>P2-C1-009-FrailtyPolypharmacyCancer/inst/frailty_concept_sets at main · darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer</t>
+  </si>
+  <si>
+    <t>Activity limitation</t>
+  </si>
+  <si>
+    <t>Anaemia and haematinic deficiency</t>
+  </si>
+  <si>
+    <t>anemia_broad</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>anemia_nutritional</t>
+  </si>
+  <si>
+    <t>Arthritis</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease (condition)</t>
+  </si>
+  <si>
+    <t>t1dm</t>
+  </si>
+  <si>
+    <t>t2dm</t>
+  </si>
+  <si>
+    <t>LongcovidVaccineEffectiveness/1_InstantiateCohorts/symptoms at main · oxford-pharmacoepi/LongcovidVaccineEffectiveness</t>
+  </si>
+  <si>
+    <t>Mike study (abaloparatide pass)</t>
+  </si>
+  <si>
+    <t>CCI</t>
+  </si>
+  <si>
+    <t>coronary_artery_disease</t>
+  </si>
+  <si>
+    <t>Parkinson's disease</t>
+  </si>
+  <si>
+    <t>COPD</t>
+  </si>
+  <si>
+    <t>Asthma</t>
+  </si>
+  <si>
+    <t>cohort</t>
+  </si>
+  <si>
+    <t>codelist</t>
+  </si>
+  <si>
+    <t>extracted_from</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>Difficulty performing personal care activity</t>
+  </si>
+  <si>
+    <t>Needs assistance with shopping</t>
+  </si>
+  <si>
+    <t>Needs help with cooking</t>
+  </si>
+  <si>
+    <t>Unable to wash self</t>
+  </si>
+  <si>
+    <t>Toilet dependency</t>
+  </si>
+  <si>
+    <t>At moderate risk of activity intolerance</t>
+  </si>
+  <si>
+    <t>At high risk of activity intolerance</t>
+  </si>
+  <si>
+    <t>Walking aid</t>
+  </si>
+  <si>
+    <t>Difficulty moving from lying to sitting</t>
+  </si>
+  <si>
+    <t>Difficulty getting off a bed</t>
+  </si>
+  <si>
+    <t>Impaired</t>
+  </si>
+  <si>
+    <t>Difficulty moving in bed</t>
+  </si>
+  <si>
+    <t>Difficulty getting on a bed</t>
+  </si>
+  <si>
+    <t>Dependent</t>
+  </si>
+  <si>
+    <t>Body disability AND/OR failure state</t>
+  </si>
+  <si>
+    <t>At increased risk for activity intolerance</t>
+  </si>
+  <si>
+    <t>Difficulty lying down</t>
+  </si>
+  <si>
+    <t>Adhesive capsulitis of shoulder</t>
+  </si>
+  <si>
+    <t>Synovitis and tenosynovitis</t>
+  </si>
+  <si>
+    <t>Capsulitis</t>
+  </si>
+  <si>
+    <t>Patellar tendonitis</t>
+  </si>
+  <si>
+    <t>Discitis</t>
+  </si>
+  <si>
+    <t>Transient synovitis</t>
+  </si>
+  <si>
+    <t>Synovitis</t>
+  </si>
+  <si>
+    <t>Transient synovitis of hip</t>
+  </si>
+  <si>
+    <t>Synovitis of knee</t>
+  </si>
+  <si>
+    <t>Lumbar discitis</t>
+  </si>
+  <si>
+    <t>Alveolitis of jaw</t>
+  </si>
+  <si>
+    <t>Infection of intervertebral disc - pyogenic</t>
+  </si>
+  <si>
+    <t>Rheumatoid vasculitis</t>
+  </si>
+  <si>
+    <t>Synovitis of hip</t>
+  </si>
+  <si>
+    <t>Thoracic discitis</t>
+  </si>
+  <si>
+    <t>Shoulder synovitis</t>
+  </si>
+  <si>
+    <t>Felty's syndrome</t>
+  </si>
+  <si>
+    <t>Cervical discitis</t>
+  </si>
+  <si>
+    <t>Synovitis of elbow</t>
+  </si>
+  <si>
+    <t>Chronic crepitant synovitis of hand and wrist</t>
+  </si>
+  <si>
+    <t>Synovitis of ankle joint</t>
+  </si>
+  <si>
+    <t>SAPHO syndrome</t>
+  </si>
+  <si>
+    <t>not sure</t>
+  </si>
+  <si>
+    <t>Synovitis of joint of foot</t>
+  </si>
+  <si>
+    <t>Iselin's disease</t>
+  </si>
+  <si>
+    <t>Osteochondritis of the talus</t>
+  </si>
+  <si>
+    <t>Juvenile osteochondrosis of head of humerus</t>
+  </si>
+  <si>
+    <t>Secondary adhesive capsulitis</t>
+  </si>
+  <si>
+    <t>Charcot's joint of foot</t>
+  </si>
+  <si>
+    <t>Synovitis and tenosynovitis of joint of wrist</t>
+  </si>
+  <si>
+    <t>Juvenile osteochondrosis of upper extremity</t>
+  </si>
+  <si>
+    <t>Juvenile osteochondrosis of capitulum of humerus</t>
+  </si>
+  <si>
+    <t>Synovitis and tenosynovitis of joint of hand</t>
+  </si>
+  <si>
+    <t>Plant thorn synovitis</t>
+  </si>
+  <si>
+    <t>Infective discitis</t>
+  </si>
+  <si>
+    <t>Synovitis/tenosynovitis - shoulder</t>
+  </si>
+  <si>
+    <t>Chronic synovitis</t>
+  </si>
+  <si>
+    <t>Otto's pelvis</t>
+  </si>
+  <si>
+    <t>Rheumatoid aortitis</t>
+  </si>
+  <si>
+    <t>Transient synovitis of right hip</t>
+  </si>
+  <si>
+    <t>Rheumatoid necrotizing vasculitis</t>
+  </si>
+  <si>
+    <t>Osteochondritis of the femoral head</t>
+  </si>
+  <si>
+    <t>Traumatic synovitis</t>
+  </si>
+  <si>
+    <t>Charcot arthropathy of midfoot</t>
+  </si>
+  <si>
+    <t>Rheumatoid carditis</t>
+  </si>
+  <si>
+    <t>Bilateral synovitis of joint of knees</t>
+  </si>
+  <si>
+    <t>Osteochondritis of metatarsal</t>
+  </si>
+  <si>
+    <t>Juvenile osteochondritis of the arm</t>
+  </si>
+  <si>
+    <t>Transient synovitis of right knee</t>
+  </si>
+  <si>
+    <t>Rheumatoid neutrophilic dermatitis</t>
+  </si>
+  <si>
+    <t>Osteochondritis of pelvis</t>
+  </si>
+  <si>
+    <t>Charcot arthropathy of joint of ankle</t>
+  </si>
+  <si>
+    <t>Transient synovitis of right wrist</t>
+  </si>
+  <si>
+    <t>Transient synovitis of right hand</t>
+  </si>
+  <si>
+    <t>Transient synovitis of left knee</t>
+  </si>
+  <si>
+    <t>Transient synovitis of left hip</t>
+  </si>
+  <si>
+    <t>Transient synovitis of left hand</t>
+  </si>
+  <si>
+    <t>Tendinitis of metatarsophalangeal joint of second toe</t>
+  </si>
+  <si>
+    <t>Temporomandibular joint capsulitis</t>
+  </si>
+  <si>
+    <t>Synovitis of right ankle joint</t>
+  </si>
+  <si>
+    <t>Synovitis of left ankle joint</t>
+  </si>
+  <si>
+    <t>Synovitis of joint of left foot</t>
+  </si>
+  <si>
+    <t>Rheumatoid scleritis</t>
+  </si>
+  <si>
+    <t>Rheumatoid pericarditis</t>
+  </si>
+  <si>
+    <t>Rheumatoid fibrosing alveolitis</t>
+  </si>
+  <si>
+    <t>Rheumatoid episcleritis</t>
+  </si>
+  <si>
+    <t>Pelvis juvenile osteochondropathy</t>
+  </si>
+  <si>
+    <t>Osteochondritis of tibial tubercle</t>
+  </si>
+  <si>
+    <t>Osteochondritis of proximal tibia</t>
+  </si>
+  <si>
+    <t>Medial epicondyle apophysitis due to overuse</t>
+  </si>
+  <si>
+    <t>Juvenile osteochondrosis of lower ulna</t>
+  </si>
+  <si>
+    <t>Juvenile osteochondrosis of head of metacarpals</t>
+  </si>
+  <si>
+    <t>Juvenile osteochondritis of the hand</t>
+  </si>
+  <si>
+    <t>Juvenile osteochondritis of the arm and hand</t>
+  </si>
+  <si>
+    <t>Juvenile osteochondritis - leg/foot</t>
+  </si>
+  <si>
+    <t>Hip juvenile osteochondropathy</t>
+  </si>
+  <si>
+    <t>Familial juvenile hyperuricemic nephropathy</t>
+  </si>
+  <si>
+    <t>Dentoalveolar cellulitis</t>
+  </si>
+  <si>
+    <t>Congenital syphilitic osteochondritis</t>
+  </si>
+  <si>
+    <t>Chronic ossifying alveolar periostitis</t>
+  </si>
+  <si>
+    <t>Adult osteochondritis of spine</t>
+  </si>
+  <si>
+    <t>Adhesive capsulitis of right shoulder</t>
+  </si>
+  <si>
+    <t>Adhesive capsulitis of left shoulder</t>
+  </si>
+  <si>
+    <t>Acute serous synovitis</t>
+  </si>
+  <si>
+    <t>Cerebral infarction due to embolism of cerebral arteries</t>
+  </si>
+  <si>
+    <t>cerebrovascular_disease</t>
+  </si>
+  <si>
+    <t>falls</t>
+  </si>
+  <si>
+    <t>Fell onto outstretched hand</t>
+  </si>
+  <si>
+    <t>Fall on or from stairs or steps</t>
+  </si>
+  <si>
+    <t>Fall from ladder</t>
+  </si>
+  <si>
+    <t>Fall on same level</t>
+  </si>
+  <si>
+    <t>Fall in home</t>
+  </si>
+  <si>
+    <t>Fall from high place</t>
+  </si>
+  <si>
+    <t>Fall from one level to another</t>
+  </si>
+  <si>
+    <t>Finding of frequency of falls</t>
+  </si>
+  <si>
+    <t>Falling injury</t>
+  </si>
+  <si>
+    <t>Fall due to loss of equilibrium</t>
+  </si>
+  <si>
+    <t>Heart failure with reduced ejection fraction due to heart valve disease</t>
+  </si>
+  <si>
+    <t>heart_valve_disorder</t>
+  </si>
+  <si>
+    <t>Atrial fibrillation due to heart valve disorder</t>
+  </si>
+  <si>
+    <t>Movement disorder</t>
+  </si>
+  <si>
+    <t>mobility_and_transfer_problems</t>
+  </si>
+  <si>
+    <t>Manual wheelchair</t>
+  </si>
+  <si>
+    <t>Mobility aid</t>
+  </si>
+  <si>
+    <t>Motorized wheelchair device</t>
+  </si>
+  <si>
+    <t>Wheelchair accessory</t>
+  </si>
+  <si>
+    <t>Care regime</t>
+  </si>
+  <si>
+    <t>Dependence on enabling machine or device</t>
+  </si>
+  <si>
+    <t>Unable to move</t>
+  </si>
+  <si>
+    <t>Unable to perform wheelchair transfers</t>
+  </si>
+  <si>
+    <t>Provision of wheelchair</t>
+  </si>
+  <si>
+    <t>peripheral_vascular_disease</t>
+  </si>
+  <si>
+    <t>Intermittent claudication due to atherosclerosis of artery of limb</t>
+  </si>
+  <si>
+    <t>Intermittent claudication of bilateral lower limbs co-occurrent and due to atherosclerosis</t>
+  </si>
+  <si>
+    <t>Intermittent claudication of left lower limb co-occurrent and due to atherosclerosis</t>
+  </si>
+  <si>
+    <t>Intermittent claudication of right lower limb co-occurrent and due to atherosclerosis</t>
+  </si>
+  <si>
+    <t>Bilateral intermittent claudication of lower limbs due to atherosclerosis of nonbiological bypass graft</t>
+  </si>
+  <si>
+    <t>Gangrene due to peripheral vascular disease</t>
+  </si>
+  <si>
+    <t>Gangrene of left lower limb due to atherosclerosis</t>
+  </si>
+  <si>
+    <t>Gangrene of right lower limb due to atherosclerosis</t>
+  </si>
+  <si>
+    <t>Peripheral gangrene</t>
+  </si>
+  <si>
+    <t>Vascular disorder of lower extremity</t>
+  </si>
+  <si>
+    <t>Vascular disorder of extremity</t>
+  </si>
+  <si>
+    <t>Ulcer of ankle due to atherosclerosis of artery of lower limb</t>
+  </si>
+  <si>
+    <t>Ulcer of calf due to atherosclerosis of artery of lower limb</t>
+  </si>
+  <si>
+    <t>Ulcer of heel due to atherosclerosis of artery of lower limb</t>
+  </si>
+  <si>
+    <t>Ischemic ulcer of left heel due to atherosclerotic disease</t>
+  </si>
+  <si>
+    <t>Ischemic ulcer of left midfoot due to atherosclerotic disease</t>
+  </si>
+  <si>
+    <t>Ischemic ulcer of right heel due to atherosclerotic disease</t>
+  </si>
+  <si>
+    <t>Ischemic ulcer of toe of left foot due to atherosclerotic disease</t>
+  </si>
+  <si>
+    <t>Ischemic ulcer of toe of right foot due to atherosclerotic disease</t>
+  </si>
+  <si>
+    <t>requirement_for_care</t>
+  </si>
+  <si>
+    <t>Care provision regime</t>
+  </si>
+  <si>
+    <t>Ankle ulcer</t>
+  </si>
+  <si>
+    <t>skin_ulcer</t>
+  </si>
+  <si>
+    <t>Chronic ulcer of ankle</t>
+  </si>
+  <si>
+    <t>Chronic ulcer of calf</t>
+  </si>
+  <si>
+    <t>Chronic ulcer of lower extremity</t>
+  </si>
+  <si>
+    <t>Chronic ulcer of sacral region</t>
+  </si>
+  <si>
+    <t>Ischemic ulcer</t>
+  </si>
+  <si>
+    <t>Mucocutaneous ulcer</t>
+  </si>
+  <si>
+    <t>Necrosis of lower leg muscle co-occurrent and due to chronic ulcer of lower leg</t>
+  </si>
+  <si>
+    <t>Right calf ulcer</t>
+  </si>
+  <si>
+    <t>Neuropathic ulcer</t>
+  </si>
+  <si>
+    <t>Neuropathic ulcer of ankle</t>
+  </si>
+  <si>
+    <t>Recurrent leg ulcer</t>
+  </si>
+  <si>
+    <t>Traumatic ulcer</t>
+  </si>
+  <si>
+    <t>Ulcer of eyelid</t>
+  </si>
+  <si>
+    <t>Ulcer of foot</t>
+  </si>
+  <si>
+    <t>Ulcer of foot due to type 1 diabetes mellitus</t>
+  </si>
+  <si>
+    <t>Ulcer of heel</t>
+  </si>
+  <si>
+    <t>Ulcer of left foot</t>
+  </si>
+  <si>
+    <t>Ulcer of lower extremity</t>
+  </si>
+  <si>
+    <t>Ulcer of lower limb due to type 2 diabetes mellitus</t>
+  </si>
+  <si>
+    <t>Ulcer of midfoot</t>
+  </si>
+  <si>
+    <t>Ulcer of mouth</t>
+  </si>
+  <si>
+    <t>Ulcer of nose</t>
+  </si>
+  <si>
+    <t>Ulcer of penis</t>
+  </si>
+  <si>
+    <t>Ulcer of right foot</t>
+  </si>
+  <si>
+    <t>Ulcer of scrotum</t>
+  </si>
+  <si>
+    <t>Ulcer of thigh</t>
+  </si>
+  <si>
+    <t>Ulcer of toe</t>
+  </si>
+  <si>
+    <t>Ulcer of toe due to type 2 diabetes mellitus</t>
+  </si>
+  <si>
+    <t>Ulceration of vulva</t>
+  </si>
+  <si>
+    <t>Ulcers of male genital organs</t>
+  </si>
+  <si>
+    <t>Acute ulcer</t>
+  </si>
+  <si>
+    <t>Chronic ulcer</t>
+  </si>
+  <si>
+    <t>Aphthous ulceration of skin and/or mucous membrane</t>
+  </si>
+  <si>
+    <t>Adult antisocial behavior</t>
+  </si>
+  <si>
+    <t>social_vulnerability</t>
+  </si>
+  <si>
+    <t>thyroid_disorders</t>
+  </si>
+  <si>
+    <t>Myxedema coma</t>
+  </si>
+  <si>
+    <t>Thyroid eye disease</t>
+  </si>
+  <si>
+    <t>Thyroid-associated dermopathy</t>
+  </si>
+  <si>
+    <t>Thyrotoxic exophthalmos</t>
+  </si>
+  <si>
+    <t>Pretibial myxedema</t>
+  </si>
+  <si>
+    <t>Thyroid acropachy</t>
+  </si>
+  <si>
+    <t>Restrictive strabismus due to Graves' disease</t>
+  </si>
+  <si>
+    <t>Poisoning by thyroid hormone</t>
+  </si>
+  <si>
+    <t>Thyrotropin overproduction</t>
+  </si>
+  <si>
+    <t>Administration of prophylactic iodine for iodine deficiency goiter</t>
+  </si>
+  <si>
+    <t>Iodine deficiency</t>
+  </si>
+  <si>
+    <t>Heart disease due to thyrotoxicosis</t>
+  </si>
+  <si>
+    <t>Heart failure due to thyrotoxicosis</t>
+  </si>
+  <si>
+    <t>Hypercalcemia due to hyperthyroidism</t>
+  </si>
+  <si>
+    <t>Myasthenic syndrome due to thyrotoxicosis</t>
+  </si>
+  <si>
+    <t>Myasthenic syndrome due to hypothyroidism</t>
+  </si>
+  <si>
+    <t>Premature puberty due to hypothyroidism</t>
+  </si>
+  <si>
+    <t>Kidney disease</t>
+  </si>
+  <si>
+    <t>Kidney lesion</t>
+  </si>
+  <si>
+    <t>Kidney stone</t>
+  </si>
+  <si>
+    <t>Cyst of kidney</t>
+  </si>
+  <si>
+    <t>Acute nephropathy</t>
+  </si>
+  <si>
+    <t>Obstructive nephropathy</t>
+  </si>
+  <si>
+    <t>Hereditary nephropathy</t>
+  </si>
+  <si>
+    <t>Hereditary nephritis</t>
+  </si>
+  <si>
+    <t>Post-infectious glomerulonephritis</t>
+  </si>
+  <si>
+    <t>Proliferative glomerulonephritis</t>
+  </si>
+  <si>
+    <t>Glomerulonephritis</t>
+  </si>
+  <si>
+    <t>Nephritic syndrome</t>
+  </si>
+  <si>
+    <t>Nephrotic syndrome</t>
+  </si>
+  <si>
+    <t>Nephritis</t>
+  </si>
+  <si>
+    <t>Tubulointerstitial nephritis</t>
+  </si>
+  <si>
+    <t>Chronic tubulointerstitial nephritis</t>
+  </si>
+  <si>
+    <t>Drug-induced tubulointerstitial nephritis</t>
+  </si>
+  <si>
+    <t>Secondary tubulointerstitial nephritis</t>
+  </si>
+  <si>
+    <t>Renal cortical necrosis</t>
+  </si>
+  <si>
+    <t>Renal impairment</t>
+  </si>
+  <si>
+    <t>Renal vascular disorder</t>
+  </si>
+  <si>
+    <t>Injury of kidney</t>
+  </si>
+  <si>
+    <t>urinary_system_disease</t>
+  </si>
+  <si>
+    <t>Blurred vision</t>
+  </si>
+  <si>
+    <t>Hazy vision</t>
+  </si>
+  <si>
+    <t>Dim vision</t>
+  </si>
+  <si>
+    <t>Homonymous hemianopia</t>
+  </si>
+  <si>
+    <t>Color blindness</t>
+  </si>
+  <si>
+    <t>Disorder of vision</t>
+  </si>
+  <si>
+    <t>Abnormal vision</t>
+  </si>
+  <si>
+    <t>visual_impairment</t>
+  </si>
+  <si>
+    <t>weight_loss_and_anorexia</t>
+  </si>
+  <si>
+    <t>Human immunodeficiency virus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -206,24 +950,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF1A1A1A"/>
-      <name val="Aptos Display"/>
-      <scheme val="major"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -235,18 +989,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -579,280 +1354,3142 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04BE1165-940E-554A-BA1E-72D36A133CAF}">
-  <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="29.125" customWidth="1"/>
     <col min="2" max="2" width="54.375" customWidth="1"/>
+    <col min="3" max="3" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A4" s="10"/>
+      <c r="B4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A10" s="10"/>
+      <c r="B10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B13" s="2"/>
+      <c r="C13" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B14" s="2"/>
+      <c r="C14" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B20" s="2"/>
+      <c r="C20" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B21" s="2"/>
+      <c r="C21" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B23" s="2"/>
+      <c r="C23" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B24" s="2"/>
+      <c r="C24" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B25" s="2"/>
+      <c r="C25" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B27" s="2"/>
+      <c r="C27" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B28" s="2"/>
+      <c r="C28" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A29" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="8"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A30" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B30" s="2"/>
+      <c r="C30" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A31" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A32" s="10"/>
+      <c r="B32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B33" s="2"/>
+      <c r="C33" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B34" s="2"/>
+      <c r="C34" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A35" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B35" s="2"/>
+      <c r="C35" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B36" s="2"/>
+      <c r="C36" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A37" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B37" s="2"/>
+      <c r="C37" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A38" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B38" s="2"/>
+      <c r="C38" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A39" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B39" s="2"/>
+      <c r="C39" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B40" s="2"/>
+      <c r="C40" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>42</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A31:A32"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C12" r:id="rId1" display="https://github.com/oxford-pharmacoepi/LongcovidVaccineEffectiveness/tree/main/1_InstantiateCohorts/symptoms" xr:uid="{2FD633F9-419D-46FC-B522-CF471E164E9A}"/>
+    <hyperlink ref="C7" r:id="rId2" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{D91A1221-F3AC-4A62-A57C-6FB482F4A6AF}"/>
+    <hyperlink ref="C5" r:id="rId3" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{6E98D8D1-1088-407B-BF91-424AEC9F522B}"/>
+    <hyperlink ref="C2" r:id="rId4" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{15CC262D-2B50-4AD5-AB31-D5F7B83CAAF3}"/>
+    <hyperlink ref="C13:C14" r:id="rId5" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{D5ED4730-C4BD-45FF-AAE0-1726318469D2}"/>
+    <hyperlink ref="C16" r:id="rId6" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{70ABDCE3-AFE2-4131-870C-C33B38266EA9}"/>
+    <hyperlink ref="C18" r:id="rId7" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{B253B20C-AF74-4383-969F-6AA31BAA021A}"/>
+    <hyperlink ref="C19" r:id="rId8" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{9FB82AEA-2C0E-4756-8F1A-AE23E6FDA49C}"/>
+    <hyperlink ref="C21" r:id="rId9" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{57974E1D-3732-4D56-BF50-C1E572C88628}"/>
+    <hyperlink ref="C23:C24" r:id="rId10" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{37E8F4CC-3A7C-4D67-80A6-795CCF269E44}"/>
+    <hyperlink ref="C28" r:id="rId11" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{8E6A937F-DD85-4E35-86FD-36660B9A157B}"/>
+    <hyperlink ref="C30" r:id="rId12" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{BEDC1C82-500D-4FA9-841E-BEE72B0EB730}"/>
+    <hyperlink ref="C33" r:id="rId13" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{124A397A-82B4-4956-ADCE-1643D3D9D29B}"/>
+    <hyperlink ref="C35" r:id="rId14" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{47935DF6-840F-46C7-A9F4-D95D2FC674E3}"/>
+    <hyperlink ref="C36" r:id="rId15" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{128416DA-648F-4C20-83FD-9C0576F7BAFB}"/>
+    <hyperlink ref="C37:C40" r:id="rId16" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{7C9ECF64-FDE3-40C5-ADA8-A25BD9F12290}"/>
+    <hyperlink ref="C11" r:id="rId17" display="https://github.com/oxford-pharmacoepi/LongcovidVaccineEffectiveness/tree/main/1_InstantiateCohorts/symptoms" xr:uid="{F6F4E119-4ECF-44F4-892F-45AC4AE62049}"/>
+    <hyperlink ref="C34" r:id="rId18" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{F656C446-54EA-4097-ABF8-6D8CC1F2DA40}"/>
+    <hyperlink ref="C27" r:id="rId19" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{732BD8AD-4E13-436A-A186-1B85AB309BF5}"/>
+    <hyperlink ref="C26" r:id="rId20" display="https://github.com/darwin-eu-studies/P2-C1-009-FrailtyPolypharmacyCancer/tree/main/inst/frailty_concept_sets" xr:uid="{B8873DF1-A706-4BA6-B60F-333DC33386FE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D5ADAA-2635-354C-81DF-96BCCB460AFA}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D147"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
+    <col min="2" max="2" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C2" s="1"/>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="3">
+        <v>4052648</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="3">
+        <v>4113164</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4044218</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="3">
+        <v>4268888</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4108025</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4012668</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="3">
+        <v>44805506</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3">
+        <v>44805505</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="3">
+        <v>4074609</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4105729</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4199868</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4125554</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="3">
+        <v>4200382</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4199866</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="3">
+        <v>4159760</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4025024</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="3">
+        <v>4215592</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4097156</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" s="3">
+        <v>4108356</v>
+      </c>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="3">
+        <v>4059015</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="3">
+        <v>4074322</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="3">
+        <v>441749</v>
+      </c>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="3">
+        <v>432803</v>
+      </c>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A25" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="3">
+        <v>4140830</v>
+      </c>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A26" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="3">
+        <v>4222734</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A27" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C27" s="3">
+        <v>4329261</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A28" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="3">
+        <v>436299</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" s="4">
+        <v>4185198</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A30" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="3">
+        <v>432787</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A31" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" s="3">
+        <v>4053866</v>
+      </c>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A32" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" s="3">
+        <v>45773075</v>
+      </c>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A33" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C33" s="3">
+        <v>37171038</v>
+      </c>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A34" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="3">
+        <v>372604</v>
+      </c>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A35" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="3">
+        <v>4045112</v>
+      </c>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A36" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4079780</v>
+      </c>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A37" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" s="3">
+        <v>4052558</v>
+      </c>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A38" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" s="3">
+        <v>45767832</v>
+      </c>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A39" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="3">
+        <v>4025024</v>
+      </c>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A40" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" s="3">
+        <v>4021166</v>
+      </c>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A41" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" s="3">
+        <v>437758</v>
+      </c>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A42" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="3">
+        <v>4021489</v>
+      </c>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A43" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" s="3">
+        <v>4119337</v>
+      </c>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A44" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C44" s="3">
+        <v>372604</v>
+      </c>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A45" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C45" s="3">
+        <v>4038881</v>
+      </c>
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A46" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C46" s="2">
+        <v>37312529</v>
+      </c>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A47" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C47" s="2">
+        <v>36717006</v>
+      </c>
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A48" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C48" s="2">
+        <v>36717286</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A49" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C49" s="2">
+        <v>36712806</v>
+      </c>
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A50" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C50" s="2">
+        <v>609009</v>
+      </c>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C51" s="2">
+        <v>44782426</v>
+      </c>
+      <c r="D51" s="2"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C52" s="2">
+        <v>36712963</v>
+      </c>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A53" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C53" s="2">
+        <v>36717279</v>
+      </c>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A54" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C54" s="2">
+        <v>4108371</v>
+      </c>
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A55" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C55" s="2">
+        <v>4189293</v>
+      </c>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A56" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C56" s="2">
+        <v>4178956</v>
+      </c>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A57" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C57" s="2">
+        <v>37312524</v>
+      </c>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A58" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C58" s="2">
+        <v>37312519</v>
+      </c>
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A59" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C59" s="2">
+        <v>37312528</v>
+      </c>
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A60" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C60" s="2">
+        <v>37159902</v>
+      </c>
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A61" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" s="2">
+        <v>37159903</v>
+      </c>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A62" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C62" s="2">
+        <v>37159905</v>
+      </c>
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A63" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C63" s="2">
+        <v>37159899</v>
+      </c>
+      <c r="D63" s="2"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A64" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C64" s="2">
+        <v>37159900</v>
+      </c>
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A65" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C65" s="3">
+        <v>4024618</v>
+      </c>
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A66" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C66" s="2">
+        <v>4171556</v>
+      </c>
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A67" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C67" s="2">
+        <v>4179675</v>
+      </c>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A68" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46270564</v>
+      </c>
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A69" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C69" s="2">
+        <v>4132314</v>
+      </c>
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A70" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C70" s="2">
+        <v>40480712</v>
+      </c>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A71" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C71" s="2">
+        <v>4029926</v>
+      </c>
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A72" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C72" s="2">
+        <v>4318377</v>
+      </c>
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A73" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C73" s="2">
+        <v>37016108</v>
+      </c>
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A74" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C74" s="2">
+        <v>4299972</v>
+      </c>
+      <c r="D74" s="2"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A75" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C75" s="2">
+        <v>46270088</v>
+      </c>
+      <c r="D75" s="2"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A76" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C76" s="2">
+        <v>44808049</v>
+      </c>
+      <c r="D76" s="2"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A77" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C77" s="2">
+        <v>37159898</v>
+      </c>
+      <c r="D77" s="2"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A78" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C78" s="2">
+        <v>4080924</v>
+      </c>
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A79" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C79" s="2">
+        <v>4196702</v>
+      </c>
+      <c r="D79" s="2"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A80" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C80" s="2">
+        <v>74719</v>
+      </c>
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A81" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C81" s="2">
+        <v>45757507</v>
+      </c>
+      <c r="D81" s="2"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A82" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C82" s="2">
+        <v>443358</v>
+      </c>
+      <c r="D82" s="2"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A83" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C83" s="2">
+        <v>3654308</v>
+      </c>
+      <c r="D83" s="2"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A84" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C84" s="2">
+        <v>197304</v>
+      </c>
+      <c r="D84" s="2"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A85" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C85" s="2">
+        <v>45757277</v>
+      </c>
+      <c r="D85" s="2"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A86" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C86" s="2">
+        <v>46269765</v>
+      </c>
+      <c r="D86" s="2"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A87" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C87" s="2">
+        <v>4094986</v>
+      </c>
+      <c r="D87" s="2"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A88" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C88" s="2">
+        <v>4214726</v>
+      </c>
+      <c r="D88" s="2"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A89" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C89" s="2">
+        <v>4294393</v>
+      </c>
+      <c r="D89" s="2"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A90" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90" s="2">
+        <v>3654309</v>
+      </c>
+      <c r="D90" s="2"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A91" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C91" s="2">
+        <v>4321736</v>
+      </c>
+      <c r="D91" s="2"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A92" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" s="2">
+        <v>443593</v>
+      </c>
+      <c r="D92" s="2"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A93" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C93" s="2">
+        <v>4103165</v>
+      </c>
+      <c r="D93" s="2"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A94" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C94" s="2">
+        <v>45757449</v>
+      </c>
+      <c r="D94" s="2"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A95" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C95" s="2">
+        <v>253815</v>
+      </c>
+      <c r="D95" s="2"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A96" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C96" s="2">
+        <v>4318848</v>
+      </c>
+      <c r="D96" s="2"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A97" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C97" s="2">
+        <v>4096339</v>
+      </c>
+      <c r="D97" s="2"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A98" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C98" s="2">
+        <v>4233476</v>
+      </c>
+      <c r="D98" s="2"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A99" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C99" s="2">
+        <v>4146449</v>
+      </c>
+      <c r="D99" s="2"/>
+    </row>
+    <row r="100" spans="1:4" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A100" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C100" s="3">
+        <v>4020464</v>
+      </c>
+      <c r="D100" s="2"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A101" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C101" s="2">
+        <v>4059416</v>
+      </c>
+      <c r="D101" s="2"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A102" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C102" s="2">
+        <v>4077943</v>
+      </c>
+      <c r="D102" s="2"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A103" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C103" s="2">
+        <v>4029587</v>
+      </c>
+      <c r="D103" s="2"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A104" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C104" s="2">
+        <v>440108</v>
+      </c>
+      <c r="D104" s="2"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A105" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C105" s="2">
+        <v>4301607</v>
+      </c>
+      <c r="D105" s="2"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A106" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C106" s="2">
+        <v>4028943</v>
+      </c>
+      <c r="D106" s="2"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A107" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C107" s="2">
+        <v>45757061</v>
+      </c>
+      <c r="D107" s="2"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A108" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C108" s="2">
+        <v>44783034</v>
+      </c>
+      <c r="D108" s="2"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A109" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C109" s="2">
+        <v>4248991</v>
+      </c>
+      <c r="D109" s="2"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A110" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C110" s="2">
+        <v>4079355</v>
+      </c>
+      <c r="D110" s="2"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A111" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C111" s="2">
+        <v>4031955</v>
+      </c>
+      <c r="D111" s="2"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A112" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C112" s="2">
+        <v>604780</v>
+      </c>
+      <c r="D112" s="2"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A113" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C113" s="2">
+        <v>619797</v>
+      </c>
+      <c r="D113" s="2"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A114" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C114" s="2">
+        <v>4329462</v>
+      </c>
+      <c r="D114" s="2"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A115" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C115" s="2">
+        <v>4101898</v>
+      </c>
+      <c r="D115" s="2"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A116" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C116" s="2">
+        <v>4102498</v>
+      </c>
+      <c r="D116" s="2"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A117" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C117" s="2">
+        <v>4099644</v>
+      </c>
+      <c r="D117" s="2"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A118" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C118" s="2">
+        <v>36716270</v>
+      </c>
+      <c r="D118" s="2"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A119" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119" s="2">
+        <v>198124</v>
+      </c>
+      <c r="D119" s="2"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A120" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C120" s="2">
+        <v>45769862</v>
+      </c>
+      <c r="D120" s="2"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A121" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C121" s="2">
+        <v>201620</v>
+      </c>
+      <c r="D121" s="2"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A122" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C122" s="2">
+        <v>4242411</v>
+      </c>
+      <c r="D122" s="2"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A123" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C123" s="2">
+        <v>4313582</v>
+      </c>
+      <c r="D123" s="2"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A124" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C124" s="2">
+        <v>4161421</v>
+      </c>
+      <c r="D124" s="2"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A125" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C125" s="2">
+        <v>45757752</v>
+      </c>
+      <c r="D125" s="2"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A126" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C126" s="2">
+        <v>4125958</v>
+      </c>
+      <c r="D126" s="2"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A127" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C127" s="2">
+        <v>40480859</v>
+      </c>
+      <c r="D127" s="2"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A128" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C128" s="2">
+        <v>4263367</v>
+      </c>
+      <c r="D128" s="2"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A129" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C129" s="2">
+        <v>4298809</v>
+      </c>
+      <c r="D129" s="2"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A130" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C130" s="2">
+        <v>195314</v>
+      </c>
+      <c r="D130" s="2"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A131" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C131" s="2">
+        <v>193253</v>
+      </c>
+      <c r="D131" s="2"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A132" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C132" s="2">
+        <v>4177206</v>
+      </c>
+      <c r="D132" s="2"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A133" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C133" s="2">
+        <v>4264718</v>
+      </c>
+      <c r="D133" s="2"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A134" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C134" s="2">
+        <v>4208918</v>
+      </c>
+      <c r="D134" s="2"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A135" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C135" s="2">
+        <v>45773214</v>
+      </c>
+      <c r="D135" s="2"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A136" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C136" s="2">
+        <v>40480627</v>
+      </c>
+      <c r="D136" s="2"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A137" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C137" s="2">
+        <v>4030518</v>
+      </c>
+      <c r="D137" s="2"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A138" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C138" s="2">
+        <v>199870</v>
+      </c>
+      <c r="D138" s="2"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A139" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C139" s="2">
+        <v>4220631</v>
+      </c>
+      <c r="D139" s="2"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A140" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C140" s="2">
+        <v>44790749</v>
+      </c>
+      <c r="D140" s="2"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A141" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C141" s="2">
+        <v>4079185</v>
+      </c>
+      <c r="D141" s="2"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A142" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C142" s="2">
+        <v>4081307</v>
+      </c>
+      <c r="D142" s="2"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A143" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C143" s="2">
+        <v>372897</v>
+      </c>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A144" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C144" s="2">
+        <v>379820</v>
+      </c>
+      <c r="D144" s="2"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A145" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C145" s="2">
+        <v>4318982</v>
+      </c>
+      <c r="D145" s="2"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A146" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C146" s="2">
+        <v>373786</v>
+      </c>
+      <c r="D146" s="2"/>
+    </row>
+    <row r="147" spans="1:4" ht="47.25" x14ac:dyDescent="0.5">
+      <c r="A147" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C147" s="3">
+        <v>4078242</v>
+      </c>
+      <c r="D147" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E7F0447-00A1-3141-8743-220EB47C2926}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D84"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="16384" width="11" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="5">
+        <v>77644</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="5">
+        <v>74728</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4287548</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="5">
+        <v>433000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="5">
+        <v>4046205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4002792</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="5">
+        <v>4168183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4199407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4083683</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4067311</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="5">
+        <v>201332</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4067312</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="5">
+        <v>4271003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="5">
+        <v>4002793</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4068628</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4035431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="5">
+        <v>81097</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="5">
+        <v>4067539</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="5">
+        <v>4079737</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="5">
+        <v>4002155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="5">
+        <v>37205177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="5">
+        <v>4245526</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="5">
+        <v>37205178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="5">
+        <v>4004615</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="5">
+        <v>4301698</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="5">
+        <v>4001987</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="5">
+        <v>4325545</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="5">
+        <v>4205084</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="57" x14ac:dyDescent="0.5">
+      <c r="A30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="5">
+        <v>37165893</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="5">
+        <v>435633</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="5">
+        <v>4147654</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="5">
+        <v>37166956</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="5">
+        <v>4001474</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" s="5">
+        <v>4120327</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="5">
+        <v>4118007</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="5">
+        <v>45766909</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" s="5">
+        <v>4344156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="5">
+        <v>4306357</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="5">
+        <v>601058</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="5">
+        <v>4347065</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="5">
+        <v>4344383</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="5">
+        <v>4083342</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" s="5">
+        <v>45763905</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="5">
+        <v>4103516</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" s="5">
+        <v>608807</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="5">
+        <v>4173164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="5">
+        <v>4344382</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" s="5">
+        <v>608805</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" s="5">
+        <v>4299308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="5">
+        <v>4145017</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="5">
+        <v>45763637</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C53" s="5">
+        <v>601059</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C54" s="5">
+        <v>601057</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="42.75" x14ac:dyDescent="0.5">
+      <c r="A55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="5">
+        <v>608806</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" s="5">
+        <v>601054</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="5">
+        <v>601053</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" s="5">
+        <v>40481591</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" s="5">
+        <v>4141507</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" s="5">
+        <v>42534871</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" s="5">
+        <v>42539217</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" s="5">
+        <v>605423</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" s="5">
+        <v>4243509</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="5">
+        <v>4296152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="5">
+        <v>4184896</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" s="5">
+        <v>4300202</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67" s="5">
+        <v>4345590</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" s="5">
+        <v>4325687</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C69" s="5">
+        <v>4328796</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A70" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70" s="5">
+        <v>45757777</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C71" s="5">
+        <v>4030389</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C72" s="5">
+        <v>4233223</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73" s="5">
+        <v>4345589</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="57" x14ac:dyDescent="0.5">
+      <c r="A74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="5">
+        <v>4145018</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" s="5">
+        <v>4117700</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76" s="5">
+        <v>4344147</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="71.25" x14ac:dyDescent="0.5">
+      <c r="A77" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C77" s="5">
+        <v>4188214</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78" s="5">
+        <v>4032731</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C79" s="5">
+        <v>4241576</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C80" s="5">
+        <v>4182394</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A81" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C81" s="5">
+        <v>4289292</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="42.75" x14ac:dyDescent="0.5">
+      <c r="A82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C82" s="5">
+        <v>762206</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="42.75" x14ac:dyDescent="0.5">
+      <c r="A83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C83" s="5">
+        <v>762207</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="28.5" x14ac:dyDescent="0.5">
+      <c r="A84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C84" s="5">
+        <v>4302975</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>